--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488082_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488082_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6446</v>
+        <v>6.7706</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6986</v>
+        <v>9.515700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.054</v>
+        <v>-2.7451</v>
       </c>
       <c r="G2" t="n">
         <v>1.4623</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1286</v>
+        <v>-0.0027</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1525</v>
+        <v>0.6647</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9762</v>
+        <v>-0.6673</v>
       </c>
       <c r="V2" t="n">
         <v>6.3021</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6113</v>
+        <v>4.2352</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1802</v>
+        <v>5.6917</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5689</v>
+        <v>-1.4566</v>
       </c>
       <c r="G3" t="n">
         <v>3.6621</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3017</v>
+        <v>0.3222</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4661</v>
+        <v>1.0454</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8356</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1367</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2755</v>
+        <v>0.7333</v>
       </c>
       <c r="E4" t="n">
-        <v>5.308</v>
+        <v>-0.0067</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0325</v>
+        <v>0.74</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.897</v>
+        <v>-0.7851</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2948</v>
+        <v>-0.7869</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3979</v>
+        <v>0.0018</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2859</v>
+        <v>0.1211</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0409</v>
+        <v>0.6797</v>
       </c>
       <c r="L4" t="n">
-        <v>0.245</v>
+        <v>-0.5586</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1828</v>
+        <v>-0.9062</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3357</v>
+        <v>-1.4666</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1529</v>
+        <v>0.5604</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1805</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6728</v>
+        <v>0.5956</v>
       </c>
       <c r="T4" t="n">
-        <v>5.0221</v>
+        <v>0.5967</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3493</v>
+        <v>-0.0011</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.6808</v>
+        <v>-0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.6808</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2231</v>
+        <v>-0.1722</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9496</v>
+        <v>0.4229</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2735</v>
+        <v>-0.5951</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7851</v>
+        <v>-0.3305</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7869</v>
+        <v>-0.1698</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0018</v>
+        <v>-0.1607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1211</v>
+        <v>0.1857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6797</v>
+        <v>0.222</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5586</v>
+        <v>-0.0363</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9062</v>
+        <v>-0.5162</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4666</v>
+        <v>-0.3918</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5604</v>
+        <v>-0.1244</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0854</v>
+        <v>0.2267</v>
       </c>
       <c r="T5" t="n">
-        <v>1.553</v>
+        <v>0.0212</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5324</v>
+        <v>0.2055</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5331</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5693</v>
+        <v>-0.7291</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.2127</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4828</v>
+        <v>-0.5165</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3305</v>
+        <v>-2.7876</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1698</v>
+        <v>-3.1186</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1607</v>
+        <v>0.331</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1857</v>
+        <v>-2.1434</v>
       </c>
       <c r="K7" t="n">
-        <v>0.222</v>
+        <v>-1.5122</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0363</v>
+        <v>-0.6312</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5162</v>
+        <v>-0.6442</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3918</v>
+        <v>-1.6064</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1244</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1704</v>
+        <v>-1.0782</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4881</v>
+        <v>-0.0255</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3178</v>
+        <v>-1.0527</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>2.3438</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>2.9474</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4737</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6929</v>
+        <v>-0.8004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1324</v>
+        <v>2.541</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8253</v>
+        <v>-3.3413</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7876</v>
+        <v>-1.897</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.1186</v>
+        <v>-2.2948</v>
       </c>
       <c r="I8" t="n">
-        <v>0.331</v>
+        <v>0.3979</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1434</v>
+        <v>0.2859</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5122</v>
+        <v>0.0409</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6312</v>
+        <v>0.245</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6442</v>
+        <v>-2.1828</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6064</v>
+        <v>-2.3357</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.1529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.042</v>
+        <v>1.5969</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3196</v>
+        <v>2.2551</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3616</v>
+        <v>-0.6582</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3438</v>
+        <v>-2.6808</v>
       </c>
       <c r="W8" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6036</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3959</v>
+        <v>-2.4625</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9788</v>
+        <v>-2.8769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5829</v>
+        <v>0.4144</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4538</v>
@@ -1156,13 +1156,13 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4684</v>
+        <v>-0.535</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3082</v>
+        <v>-0.2063</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1602</v>
+        <v>-0.3287</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0415</v>
+        <v>-3.3242</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8275</v>
+        <v>-2.1101</v>
       </c>
       <c r="F10" t="n">
         <v>-1.214</v>
@@ -1234,10 +1234,10 @@
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7012</v>
+        <v>0.4185</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2593</v>
+        <v>0.9766</v>
       </c>
       <c r="U10" t="n">
         <v>-0.5581</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9834</v>
+        <v>-4.5093</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2686</v>
+        <v>-4.9629</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2852</v>
+        <v>0.4536</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4356</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2129</v>
+        <v>-0.7388</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6129</v>
+        <v>-0.3073</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5999</v>
+        <v>-0.4314</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5331</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8222</v>
+        <v>-4.5559</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2898</v>
+        <v>-3.2482</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5323</v>
+        <v>-1.3077</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9038</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4029</v>
+        <v>-0.1367</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7377</v>
+        <v>0.3039</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6652</v>
+        <v>-0.4406</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5331</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.952499999999999</v>
+        <v>-5.0163</v>
       </c>
       <c r="E13" t="n">
-        <v>3.817600000000002</v>
+        <v>4.753799999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.77</v>
+        <v>-9.770100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-12.2599</v>
@@ -1438,13 +1438,13 @@
         <v>-10.7876</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.472399999999999</v>
+        <v>-1.4724</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1319</v>
+        <v>-2.131899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>3.529300000000001</v>
+        <v>3.5293</v>
       </c>
       <c r="L13" t="n">
         <v>-5.6611</v>
@@ -1468,10 +1468,10 @@
         <v>15.8578</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4033000000000007</v>
+        <v>0.5327</v>
       </c>
       <c r="T13" t="n">
-        <v>4.388500000000001</v>
+        <v>5.3245</v>
       </c>
       <c r="U13" t="n">
         <v>-4.791700000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.0989</v>
+        <v>14.6494</v>
       </c>
       <c r="E14" t="n">
-        <v>14.709</v>
+        <v>14.9127</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6101</v>
+        <v>-0.2634</v>
       </c>
       <c r="G14" t="n">
         <v>13.3915</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0835</v>
+        <v>0.467</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5692</v>
+        <v>0.7729</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6526</v>
+        <v>-0.3059</v>
       </c>
       <c r="V14" t="n">
         <v>0.1962</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.33</v>
+        <v>2.8842</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8878</v>
+        <v>1.5635</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4421</v>
+        <v>1.3207</v>
       </c>
       <c r="G15" t="n">
         <v>2.528</v>
@@ -1624,13 +1624,13 @@
         <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8874</v>
+        <v>1.4417</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2211</v>
+        <v>0.8968</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6663</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>2.6808</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3033</v>
+        <v>1.841</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5058</v>
+        <v>-0.0036</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7976</v>
+        <v>1.8446</v>
       </c>
       <c r="G16" t="n">
         <v>1.9216</v>
@@ -1702,13 +1702,13 @@
         <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>1.245</v>
+        <v>0.7827</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2373</v>
+        <v>0.7279</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0078</v>
+        <v>0.0548</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0704</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LEGANOVIC</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.925</v>
+        <v>1.5073</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5745</v>
+        <v>3.6045</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3505</v>
+        <v>-2.0972</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2475</v>
+        <v>0.6014</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5192</v>
+        <v>1.6747</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2717</v>
+        <v>-1.0734</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.659</v>
+        <v>0.7472</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.659</v>
+        <v>2.664</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.9169</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4114</v>
+        <v>-0.1458</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1398</v>
+        <v>-0.9893</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2717</v>
+        <v>0.8435</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1725</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2335</v>
+        <v>0.247</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0609</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.6104</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>J. LEGANOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2934</v>
+        <v>0.2223</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2989</v>
+        <v>-0.2404</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0055</v>
+        <v>0.4628</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6014</v>
+        <v>-0.2475</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6747</v>
+        <v>-0.5192</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0734</v>
+        <v>0.2717</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7472</v>
+        <v>-0.659</v>
       </c>
       <c r="K19" t="n">
-        <v>2.664</v>
+        <v>-0.659</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9169</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1458</v>
+        <v>0.4114</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9893</v>
+        <v>0.1398</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8435</v>
+        <v>0.2717</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8233</v>
+        <v>0.4699</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0586</v>
+        <v>0.4185</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.7647</v>
+        <v>0.0514</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6104</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1269</v>
+        <v>0.0488</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0957</v>
+        <v>-0.892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9688</v>
+        <v>0.9408</v>
       </c>
       <c r="G20" t="n">
         <v>0.6334</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0326</v>
+        <v>0.2083</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>0.0789</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1574</v>
+        <v>0.1294</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1401</v>
+        <v>-0.8133</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0684</v>
+        <v>1.1516</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2085</v>
+        <v>-1.9649</v>
       </c>
       <c r="G21" t="n">
         <v>0.4244</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0569</v>
+        <v>0.3836</v>
       </c>
       <c r="T21" t="n">
-        <v>1.674</v>
+        <v>0.7572</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6172</v>
+        <v>-0.3736</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4142</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1239</v>
+        <v>-0.864</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7171</v>
+        <v>0.9208</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8409</v>
+        <v>-1.7848</v>
       </c>
       <c r="G22" t="n">
         <v>0.1082</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2232</v>
+        <v>0.0367</v>
       </c>
       <c r="T22" t="n">
-        <v>0.011</v>
+        <v>0.2148</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9651</v>
+        <v>-1.8785</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3668</v>
+        <v>-2.5519</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4017</v>
+        <v>0.6734</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6472</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9215</v>
+        <v>0.1651</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4881</v>
+        <v>0.3268</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4333</v>
+        <v>-0.1617</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. FIDALGO PEDUZZI</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.789</v>
+        <v>-2.7566</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8014</v>
+        <v>-2.4536</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0124</v>
+        <v>-0.3029</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.495</v>
+        <v>-3.9425</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0024</v>
+        <v>-2.4617</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4974</v>
+        <v>-1.4809</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2575</v>
+        <v>-3.591</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0605</v>
+        <v>-1.6742</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3181</v>
+        <v>-1.9169</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7625999999999999</v>
+        <v>-0.3515</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0581</v>
+        <v>-0.7875</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8207</v>
+        <v>0.436</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3876</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6993</v>
+        <v>0.3753</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5616</v>
+        <v>0.4388</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1377</v>
+        <v>-0.0635</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2071</v>
+        <v>1.2071</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>A. FIDALGO PEDUZZI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8268</v>
+        <v>-3.1392</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0649</v>
+        <v>-3.292</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.762</v>
+        <v>0.1528</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.9425</v>
+        <v>-0.495</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4617</v>
+        <v>0.0024</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4809</v>
+        <v>-0.4974</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.591</v>
+        <v>-1.2575</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6742</v>
+        <v>0.0605</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9169</v>
+        <v>-1.3181</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3515</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7875</v>
+        <v>-0.0581</v>
       </c>
       <c r="O25" t="n">
-        <v>0.436</v>
+        <v>0.8207</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.695</v>
+        <v>-0.0496</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1724</v>
+        <v>-0.0522</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5226</v>
+        <v>0.0027</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2071</v>
+        <v>-1.2071</v>
       </c>
       <c r="W25" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4737</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3292</v>
+        <v>-3.3353</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.9654</v>
+        <v>-3.2523</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3638</v>
+        <v>-0.083</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3189</v>
@@ -2482,13 +2482,13 @@
         <v>0.7929</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5455</v>
+        <v>-0.5516</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7488</v>
+        <v>-0.0357</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7967</v>
+        <v>-0.5159</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2666</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>5.952300000000001</v>
+        <v>8.668800000000001</v>
       </c>
       <c r="E27" t="n">
         <v>9.769999999999996</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.817700000000001</v>
+        <v>-1.1011</v>
       </c>
       <c r="G27" t="n">
         <v>12.2601</v>
@@ -2530,7 +2530,7 @@
         <v>10.7875</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4723</v>
+        <v>1.472300000000001</v>
       </c>
       <c r="J27" t="n">
         <v>10.1281</v>
@@ -2542,7 +2542,7 @@
         <v>-4.1888</v>
       </c>
       <c r="M27" t="n">
-        <v>2.131999999999999</v>
+        <v>2.132</v>
       </c>
       <c r="N27" t="n">
         <v>-3.5293</v>
@@ -2551,7 +2551,7 @@
         <v>5.6612</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.955499999999999</v>
+        <v>-4.9555</v>
       </c>
       <c r="Q27" t="n">
         <v>-15.8577</v>
@@ -2560,13 +2560,13 @@
         <v>10.9022</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4031000000000002</v>
+        <v>3.1197</v>
       </c>
       <c r="T27" t="n">
-        <v>4.791799999999999</v>
+        <v>4.791699999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.388400000000001</v>
+        <v>-1.6719</v>
       </c>
       <c r="V27" t="n">
         <v>-1.7553</v>
